--- a/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/02_RR2 - Risk Aksiyonları ve Türev Akışlar/EKG-PRJ-FRM-30_pfmea_gozden_gecirme_tutanagi_ve_reaktif_5_neden_formu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/02_RR2 - Risk Aksiyonları ve Türev Akışlar/EKG-PRJ-FRM-30_pfmea_gozden_gecirme_tutanagi_ve_reaktif_5_neden_formu.xlsx
@@ -869,7 +869,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-30&amp;C&amp;"Arial,Regular"&amp;11PFMEA Gözden Geçirme Tutanağı ve Reaktif 5 Neden Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Tork örneği kaldırıldı; kanıta dayalı oluşum/kaçış kök nedeni ve etkinlik takibi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1154,7 +1155,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-FRM-30&amp;C&amp;"Arial,Regular"&amp;11PFMEA Gözden Geçirme Tutanağı ve Reaktif 5 Neden Formu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 11.06.2026 | Revizyon: 23.09.2026
+Revizyon nedeni: Tork örneği kaldırıldı; kanıta dayalı oluşum/kaçış kök nedeni ve etkinlik takibi eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>